--- a/5-2026.xlsx
+++ b/5-2026.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CB8860-8696-4961-A94C-F7403B1BC8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14CF326-BA85-40EE-8870-9B16B4D784CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{C7DBF94B-76D0-4DB1-B5F9-1612F1925133}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{C7DBF94B-76D0-4DB1-B5F9-1612F1925133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$AA$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="22">
   <si>
     <t>الاصول الثابته بالصافي :</t>
   </si>
@@ -117,7 +122,7 @@
     <numFmt numFmtId="164" formatCode="m\-yyyy"/>
     <numFmt numFmtId="165" formatCode="B1mmm\-yy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +195,14 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -278,7 +291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -331,6 +344,9 @@
     <xf numFmtId="3" fontId="9" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="10" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -347,6 +363,242 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="قائمة الدخل"/>
+      <sheetName val="ميزانيه"/>
+      <sheetName val="الايضاحات"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="36">
+          <cell r="O36">
+            <v>1803626.7499999756</v>
+          </cell>
+          <cell r="Q36">
+            <v>10102344.589999976</v>
+          </cell>
+          <cell r="S36">
+            <v>13372462.680000003</v>
+          </cell>
+          <cell r="U36">
+            <v>7088687.7199999718</v>
+          </cell>
+          <cell r="W36">
+            <v>6033176.7500000028</v>
+          </cell>
+          <cell r="Y36">
+            <v>5096691.0900000576</v>
+          </cell>
+          <cell r="AA36">
+            <v>19013087.240000173</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="10">
+          <cell r="P10">
+            <v>28287588.039999999</v>
+          </cell>
+          <cell r="R10">
+            <v>27663588.039999999</v>
+          </cell>
+          <cell r="T10">
+            <v>27663588.039999999</v>
+          </cell>
+          <cell r="V10">
+            <v>25264504.039999999</v>
+          </cell>
+          <cell r="X10">
+            <v>25264504.039999999</v>
+          </cell>
+          <cell r="Z10">
+            <v>25264504.039999999</v>
+          </cell>
+          <cell r="AB10">
+            <v>25264504.039999999</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="P13">
+            <v>22199177.149999999</v>
+          </cell>
+          <cell r="R13">
+            <v>21766987.909999996</v>
+          </cell>
+          <cell r="T13">
+            <v>21958105.329999998</v>
+          </cell>
+          <cell r="V13">
+            <v>19733077.309999999</v>
+          </cell>
+          <cell r="X13">
+            <v>19903916.759999998</v>
+          </cell>
+          <cell r="Z13">
+            <v>20074784.07</v>
+          </cell>
+          <cell r="AB13">
+            <v>20245724.849999998</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="P23">
+            <v>14943580.889999989</v>
+          </cell>
+          <cell r="R23">
+            <v>13711093.810000001</v>
+          </cell>
+          <cell r="T23">
+            <v>16704395.5</v>
+          </cell>
+          <cell r="V23">
+            <v>7370521.9300000072</v>
+          </cell>
+          <cell r="X23">
+            <v>22488344.050000008</v>
+          </cell>
+          <cell r="Z23">
+            <v>40175935.459999979</v>
+          </cell>
+          <cell r="AB23">
+            <v>48312473.840000004</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="P39">
+            <v>-0.30999999865889549</v>
+          </cell>
+          <cell r="R39">
+            <v>-0.30999999865889549</v>
+          </cell>
+          <cell r="T39">
+            <v>-0.30999999865889549</v>
+          </cell>
+          <cell r="V39">
+            <v>-0.30999999865889549</v>
+          </cell>
+          <cell r="X39">
+            <v>-0.30999999865889549</v>
+          </cell>
+          <cell r="Z39">
+            <v>-0.30999999865889549</v>
+          </cell>
+          <cell r="AB39">
+            <v>-0.30999999865889499</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="P49">
+            <v>21865000.519999959</v>
+          </cell>
+          <cell r="R49">
+            <v>54827135.009999961</v>
+          </cell>
+          <cell r="T49">
+            <v>41244559.470000014</v>
+          </cell>
+          <cell r="V49">
+            <v>31136322.539999995</v>
+          </cell>
+          <cell r="X49">
+            <v>9514470.6399999894</v>
+          </cell>
+          <cell r="Z49">
+            <v>10873933.310000006</v>
+          </cell>
+          <cell r="AB49">
+            <v>30131838.569999985</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="R59">
+            <v>3416615.87</v>
+          </cell>
+          <cell r="T59">
+            <v>3637923.2</v>
+          </cell>
+          <cell r="V59">
+            <v>3637923.2</v>
+          </cell>
+          <cell r="X59">
+            <v>3404110.7</v>
+          </cell>
+          <cell r="Z59">
+            <v>3636923.24</v>
+          </cell>
+          <cell r="AB59">
+            <v>3636923.24</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="X69">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="P90">
+            <v>457416.99000000948</v>
+          </cell>
+          <cell r="R90">
+            <v>452680.99000000948</v>
+          </cell>
+          <cell r="T90">
+            <v>422675.99000000948</v>
+          </cell>
+          <cell r="V90">
+            <v>391625.81999999279</v>
+          </cell>
+          <cell r="X90">
+            <v>134813.46000000829</v>
+          </cell>
+          <cell r="Z90">
+            <v>-321246.90000000602</v>
+          </cell>
+          <cell r="AB90">
+            <v>4.6100000143051147</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="X104">
+            <v>0</v>
+          </cell>
+          <cell r="Z104">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="P112">
+            <v>12923.44</v>
+          </cell>
+          <cell r="R112">
+            <v>12923.44</v>
+          </cell>
+          <cell r="T112">
+            <v>12923.44</v>
+          </cell>
+          <cell r="V112">
+            <v>12923.44</v>
+          </cell>
+          <cell r="X112">
+            <v>12923.44</v>
+          </cell>
+          <cell r="Z112">
+            <v>12923.44</v>
+          </cell>
+          <cell r="AB112">
+            <v>12923.44</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -646,428 +898,600 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4E14BED-4A82-49F0-AB48-4A735E1CAC39}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2">
+        <v>46174</v>
+      </c>
+      <c r="C1" s="2">
         <v>46143</v>
       </c>
-      <c r="C1" s="2">
+      <c r="D1" s="2">
         <v>46113</v>
       </c>
-      <c r="D1" s="2">
+      <c r="E1" s="2">
         <v>46082</v>
       </c>
-      <c r="E1" s="2">
+      <c r="F1" s="2">
         <v>46054</v>
       </c>
-      <c r="F1" s="2">
+      <c r="G1" s="2">
         <v>46023</v>
       </c>
-      <c r="G1" s="2">
+      <c r="H1" s="2">
         <v>45992</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>21766987.909999996</v>
+        <f>[1]الايضاحات!P10</f>
+        <v>28287588.039999999</v>
       </c>
       <c r="C2" s="4">
-        <v>21958105.329999998</v>
-      </c>
-      <c r="D2" s="5">
-        <v>19733077.309999999</v>
+        <f>[1]الايضاحات!R10</f>
+        <v>27663588.039999999</v>
+      </c>
+      <c r="D2" s="4">
+        <f>[1]الايضاحات!T10</f>
+        <v>27663588.039999999</v>
       </c>
       <c r="E2" s="5">
-        <v>19903916.759999998</v>
+        <f>[1]الايضاحات!V10</f>
+        <v>25264504.039999999</v>
       </c>
       <c r="F2" s="5">
-        <v>20074784.07</v>
-      </c>
-      <c r="G2" s="6">
-        <v>20245724.849999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X10</f>
+        <v>25264504.039999999</v>
+      </c>
+      <c r="G2" s="5">
+        <f>[1]الايضاحات!Z10</f>
+        <v>25264504.039999999</v>
+      </c>
+      <c r="H2" s="6">
+        <f>[1]الايضاحات!AB10</f>
+        <v>25264504.039999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7">
-        <v>2357614.15</v>
+        <f>[1]الايضاحات!P12</f>
+        <v>0</v>
       </c>
       <c r="C3" s="7">
-        <v>2346114.15</v>
-      </c>
-      <c r="D3" s="8">
-        <v>2232984.15</v>
+        <f>[1]الايضاحات!R12</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <f>[1]الايضاحات!T12</f>
+        <v>0</v>
       </c>
       <c r="E3" s="8">
-        <v>2200362.15</v>
+        <f>[1]الايضاحات!V12</f>
+        <v>0</v>
       </c>
       <c r="F3" s="8">
-        <v>1884602.5</v>
-      </c>
-      <c r="G3" s="9">
-        <v>1884602.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X12</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="8">
+        <f>[1]الايضاحات!Z12</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <f>[1]الايضاحات!AB12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="7">
-        <v>596741</v>
+        <f>[1]الايضاحات!P13</f>
+        <v>22199177.149999999</v>
       </c>
       <c r="C4" s="7">
-        <v>596741</v>
-      </c>
-      <c r="D4" s="8">
-        <v>596741</v>
+        <f>[1]الايضاحات!R13</f>
+        <v>21766987.909999996</v>
+      </c>
+      <c r="D4" s="7">
+        <f>[1]الايضاحات!T13</f>
+        <v>21958105.329999998</v>
       </c>
       <c r="E4" s="8">
-        <v>596741</v>
+        <f>[1]الايضاحات!V13</f>
+        <v>19733077.309999999</v>
       </c>
       <c r="F4" s="8">
-        <v>596741</v>
-      </c>
-      <c r="G4" s="9">
-        <v>596741</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X13</f>
+        <v>19903916.759999998</v>
+      </c>
+      <c r="G4" s="8">
+        <f>[1]الايضاحات!Z13</f>
+        <v>20074784.07</v>
+      </c>
+      <c r="H4" s="9">
+        <f>[1]الايضاحات!AB13</f>
+        <v>20245724.849999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11">
-        <v>24721343.059999995</v>
+        <f>SUM(B2:B4)</f>
+        <v>50486765.189999998</v>
       </c>
       <c r="C5" s="11">
-        <v>24900960.479999997</v>
-      </c>
-      <c r="D5" s="12">
-        <v>22562802.459999997</v>
+        <f>SUM(C2:C4)</f>
+        <v>49430575.949999996</v>
+      </c>
+      <c r="D5" s="11">
+        <f>SUM(D2:D4)</f>
+        <v>49621693.369999997</v>
       </c>
       <c r="E5" s="12">
-        <v>22701019.909999996</v>
+        <f>SUM(E2:E4)</f>
+        <v>44997581.349999994</v>
       </c>
       <c r="F5" s="12">
-        <v>22556127.57</v>
+        <f>SUM(F2:F4)</f>
+        <v>45168420.799999997</v>
       </c>
       <c r="G5" s="12">
-        <v>22727068.349999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <f>SUM(G2:G4)</f>
+        <v>45339288.109999999</v>
+      </c>
+      <c r="H5" s="12">
+        <f>SUM(H2:H4)</f>
+        <v>45510228.890000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="7">
-        <v>307973482.93999964</v>
+        <f>[1]الايضاحات!P23</f>
+        <v>14943580.889999989</v>
       </c>
       <c r="C6" s="7">
-        <v>251497026.58999956</v>
-      </c>
-      <c r="D6" s="8">
-        <v>216736145.83000022</v>
+        <f>[1]الايضاحات!R23</f>
+        <v>13711093.810000001</v>
+      </c>
+      <c r="D6" s="7">
+        <f>[1]الايضاحات!T23</f>
+        <v>16704395.5</v>
       </c>
       <c r="E6" s="8">
-        <v>246421191.35999998</v>
+        <f>[1]الايضاحات!V23</f>
+        <v>7370521.9300000072</v>
       </c>
       <c r="F6" s="8">
-        <v>276755395.22999948</v>
-      </c>
-      <c r="G6" s="9">
-        <v>263703635.98999962</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X23</f>
+        <v>22488344.050000008</v>
+      </c>
+      <c r="G6" s="8">
+        <f>[1]الايضاحات!Z23</f>
+        <v>40175935.459999979</v>
+      </c>
+      <c r="H6" s="9">
+        <f>[1]الايضاحات!AB23</f>
+        <v>48312473.840000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>53595675.89000012</v>
+        <f>[1]الايضاحات!P39</f>
+        <v>-0.30999999865889549</v>
       </c>
       <c r="C7" s="7">
-        <v>35170513.56999974</v>
-      </c>
-      <c r="D7" s="8">
-        <v>36391015.480000034</v>
+        <f>[1]الايضاحات!R39</f>
+        <v>-0.30999999865889549</v>
+      </c>
+      <c r="D7" s="7">
+        <f>[1]الايضاحات!T39</f>
+        <v>-0.30999999865889549</v>
       </c>
       <c r="E7" s="8">
-        <v>35044469.309999794</v>
+        <f>[1]الايضاحات!V39</f>
+        <v>-0.30999999865889549</v>
       </c>
       <c r="F7" s="8">
-        <v>40312392.319999546</v>
-      </c>
-      <c r="G7" s="9">
-        <v>35899338.66000022</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X39</f>
+        <v>-0.30999999865889549</v>
+      </c>
+      <c r="G7" s="8">
+        <f>[1]الايضاحات!Z39</f>
+        <v>-0.30999999865889549</v>
+      </c>
+      <c r="H7" s="9">
+        <f>[1]الايضاحات!AB39</f>
+        <v>-0.30999999865889499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="7">
-        <v>88773553.039999709</v>
+        <f>[1]الايضاحات!P49</f>
+        <v>21865000.519999959</v>
       </c>
       <c r="C8" s="7">
-        <v>80049672.870000184</v>
-      </c>
-      <c r="D8" s="8">
-        <v>69103414.059999168</v>
+        <f>[1]الايضاحات!R49</f>
+        <v>54827135.009999961</v>
+      </c>
+      <c r="D8" s="7">
+        <f>[1]الايضاحات!T49</f>
+        <v>41244559.470000014</v>
       </c>
       <c r="E8" s="8">
-        <v>62152170.890000343</v>
+        <f>[1]الايضاحات!V49</f>
+        <v>31136322.539999995</v>
       </c>
       <c r="F8" s="8">
-        <v>73211384.189999923</v>
-      </c>
-      <c r="G8" s="9">
-        <v>55796550.240000226</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X49</f>
+        <v>9514470.6399999894</v>
+      </c>
+      <c r="G8" s="8">
+        <f>[1]الايضاحات!Z49</f>
+        <v>10873933.310000006</v>
+      </c>
+      <c r="H8" s="9">
+        <f>[1]الايضاحات!AB49</f>
+        <v>30131838.569999985</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>144670090.74999979</v>
+        <f>[1]الايضاحات!P53</f>
+        <v>0</v>
       </c>
       <c r="C9" s="7">
-        <v>122145542.94999963</v>
-      </c>
-      <c r="D9" s="8">
-        <v>111928881.3599996</v>
+        <f>[1]الايضاحات!R53</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="7">
+        <f>[1]الايضاحات!T53</f>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>109562688.63999996</v>
+        <f>[1]الايضاحات!V53</f>
+        <v>0</v>
       </c>
       <c r="F9" s="8">
-        <v>125746266.17999986</v>
-      </c>
-      <c r="G9" s="9">
-        <v>137039113.50999942</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X53</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <f>[1]الايضاحات!Z53</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <f>[1]الايضاحات!AB53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="7">
+        <v>3637923.2</v>
+      </c>
+      <c r="C10" s="7">
+        <f>[1]الايضاحات!R59</f>
         <v>3416615.87</v>
       </c>
-      <c r="C10" s="7">
+      <c r="D10" s="7">
+        <f>[1]الايضاحات!T59</f>
         <v>3637923.2</v>
       </c>
-      <c r="D10" s="8">
+      <c r="E10" s="8">
+        <f>[1]الايضاحات!V59</f>
         <v>3637923.2</v>
       </c>
-      <c r="E10" s="8">
+      <c r="F10" s="8">
+        <f>[1]الايضاحات!X59</f>
         <v>3404110.7</v>
       </c>
-      <c r="F10" s="8">
+      <c r="G10" s="8">
+        <f>[1]الايضاحات!Z59</f>
         <v>3636923.24</v>
       </c>
-      <c r="G10" s="9">
-        <v>4006885.54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="H10" s="9">
+        <f>[1]الايضاحات!AB59</f>
+        <v>3636923.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="11">
-        <v>598429418.48999929</v>
+        <f>SUM(B6:B10)</f>
+        <v>40446504.299999952</v>
       </c>
       <c r="C11" s="11">
-        <v>492500679.17999911</v>
-      </c>
-      <c r="D11" s="12">
-        <v>437797379.92999899</v>
+        <f>SUM(C6:C10)</f>
+        <v>71954844.379999965</v>
+      </c>
+      <c r="D11" s="11">
+        <f>SUM(D6:D10)</f>
+        <v>61586877.860000014</v>
       </c>
       <c r="E11" s="12">
-        <v>456584630.90000004</v>
+        <f>SUM(E6:E10)</f>
+        <v>42144767.360000007</v>
       </c>
       <c r="F11" s="12">
-        <v>519662361.15999877</v>
+        <f>SUM(F6:F10)</f>
+        <v>35406925.079999998</v>
       </c>
       <c r="G11" s="12">
-        <v>496445523.93999952</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+        <f>SUM(G6:G10)</f>
+        <v>54686791.699999981</v>
+      </c>
+      <c r="H11" s="12">
+        <f>SUM(H6:H10)</f>
+        <v>82081235.339999989</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="14">
-        <v>623150761.54999924</v>
-      </c>
-      <c r="C12" s="15">
-        <v>517401639.65999913</v>
+        <f>B11+B5</f>
+        <v>90933269.48999995</v>
+      </c>
+      <c r="C12" s="14">
+        <f>C11+C5</f>
+        <v>121385420.32999995</v>
       </c>
       <c r="D12" s="15">
-        <v>460360182.38999897</v>
+        <f>D5+D11</f>
+        <v>111208571.23000002</v>
       </c>
       <c r="E12" s="15">
-        <v>479285650.81000006</v>
+        <f>E11+E5</f>
+        <v>87142348.710000008</v>
       </c>
       <c r="F12" s="15">
-        <v>542218488.72999883</v>
+        <f>F11+F5</f>
+        <v>80575345.879999995</v>
       </c>
       <c r="G12" s="15">
-        <v>519172592.28999954</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <f>G11+G5</f>
+        <v>100026079.80999997</v>
+      </c>
+      <c r="H12" s="15">
+        <f>H5+H11</f>
+        <v>127591464.22999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>221490803.47</v>
+        <f>[1]الايضاحات!P69</f>
+        <v>0</v>
       </c>
       <c r="C13" s="7">
-        <v>120354247.44999973</v>
-      </c>
-      <c r="D13" s="8">
-        <v>105458756.66999979</v>
+        <f>[1]الايضاحات!R69</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="7">
+        <f>[1]الايضاحات!T69</f>
+        <v>0</v>
       </c>
       <c r="E13" s="8">
-        <v>133665877.53000003</v>
+        <f>[1]الايضاحات!V69</f>
+        <v>0</v>
       </c>
       <c r="F13" s="8">
-        <v>177227503.53999999</v>
-      </c>
-      <c r="G13" s="9">
-        <v>148043033.26000029</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X69</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <f>[1]الايضاحات!Z69</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <f>[1]الايضاحات!AB69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>17987661.130000044</v>
+        <f>[1]الايضاحات!P90</f>
+        <v>457416.99000000948</v>
       </c>
       <c r="C14" s="7">
-        <v>24918653.62000002</v>
-      </c>
-      <c r="D14" s="8">
-        <v>21895527.219999943</v>
+        <f>[1]الايضاحات!R90</f>
+        <v>452680.99000000948</v>
+      </c>
+      <c r="D14" s="7">
+        <f>[1]الايضاحات!T90</f>
+        <v>422675.99000000948</v>
       </c>
       <c r="E14" s="8">
-        <v>24608773.970000006</v>
+        <f>[1]الايضاحات!V90</f>
+        <v>391625.81999999279</v>
       </c>
       <c r="F14" s="8">
-        <v>28574676.589999989</v>
-      </c>
-      <c r="G14" s="9">
-        <v>26189842.269999973</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X90</f>
+        <v>134813.46000000829</v>
+      </c>
+      <c r="G14" s="8">
+        <f>[1]الايضاحات!Z90</f>
+        <v>-321246.90000000602</v>
+      </c>
+      <c r="H14" s="9">
+        <f>[1]الايضاحات!AB90</f>
+        <v>4.6100000143051147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>104414415.23000011</v>
+        <f>[1]الايضاحات!P104</f>
+        <v>0</v>
       </c>
       <c r="C15" s="7">
-        <v>102984255.44000015</v>
-      </c>
-      <c r="D15" s="8">
-        <v>77233877.720000073</v>
+        <f>[1]الايضاحات!R104</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="7">
+        <f>[1]الايضاحات!T104</f>
+        <v>0</v>
       </c>
       <c r="E15" s="8">
-        <v>72327612.63000001</v>
+        <f>[1]الايضاحات!V104</f>
+        <v>0</v>
       </c>
       <c r="F15" s="8">
-        <v>93766086.059999973</v>
-      </c>
-      <c r="G15" s="9">
-        <v>107449108.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X104</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <f>[1]الايضاحات!Z104</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <f>[1]الايضاحات!AB104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="8">
+        <f>727553+59413</f>
         <v>786966</v>
       </c>
       <c r="C16" s="8">
+        <f>727553+59413</f>
         <v>786966</v>
       </c>
       <c r="D16" s="8">
+        <f>727553+59413</f>
         <v>786966</v>
       </c>
       <c r="E16" s="8">
+        <f>727553+59413</f>
         <v>786966</v>
       </c>
       <c r="F16" s="8">
+        <f>727553+59413</f>
         <v>786966</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
+        <f>727553+59413</f>
         <v>786966</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" s="9">
+        <f>727553+59413</f>
+        <v>786966</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="7">
-        <v>517679.65000000049</v>
+        <f>[1]الايضاحات!P112</f>
+        <v>12923.44</v>
       </c>
       <c r="C17" s="7">
-        <v>517679.4700000005</v>
-      </c>
-      <c r="D17" s="8">
-        <v>517679.64999807166</v>
+        <f>[1]الايضاحات!R112</f>
+        <v>12923.44</v>
+      </c>
+      <c r="D17" s="7">
+        <f>[1]الايضاحات!T112</f>
+        <v>12923.44</v>
       </c>
       <c r="E17" s="8">
-        <v>517679.6499998002</v>
+        <f>[1]الايضاحات!V112</f>
+        <v>12923.44</v>
       </c>
       <c r="F17" s="8">
-        <v>517692.1599990754</v>
-      </c>
-      <c r="G17" s="9">
-        <v>454768.86000001483</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
+        <f>[1]الايضاحات!X112</f>
+        <v>12923.44</v>
+      </c>
+      <c r="G17" s="8">
+        <f>[1]الايضاحات!Z112</f>
+        <v>12923.44</v>
+      </c>
+      <c r="H17" s="9">
+        <f>[1]الايضاحات!AB112</f>
+        <v>12923.44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="11">
-        <v>345197525.48000014</v>
+        <f>SUM(B13:B17)</f>
+        <v>1257306.4300000095</v>
       </c>
       <c r="C18" s="11">
-        <v>249561801.9799999</v>
-      </c>
-      <c r="D18" s="12">
-        <v>205892807.25999787</v>
+        <f>SUM(C13:C17)</f>
+        <v>1252570.4300000095</v>
+      </c>
+      <c r="D18" s="11">
+        <f>SUM(D13:D17)</f>
+        <v>1222565.4300000095</v>
       </c>
       <c r="E18" s="12">
-        <v>231906909.77999985</v>
+        <f>SUM(E13:E17)</f>
+        <v>1191515.2599999928</v>
       </c>
       <c r="F18" s="12">
-        <v>300872924.34999901</v>
+        <f>SUM(F13:F17)</f>
+        <v>934702.90000000829</v>
       </c>
       <c r="G18" s="12">
-        <v>282923719.14000028</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <f>SUM(G13:G17)</f>
+        <v>478642.53999999398</v>
+      </c>
+      <c r="H18" s="12">
+        <f>SUM(H13:H17)</f>
+        <v>799894.05000001425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1077,7 +1501,7 @@
       <c r="C19" s="7">
         <v>8000000</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>8000000</v>
       </c>
       <c r="E19" s="8">
@@ -1086,11 +1510,14 @@
       <c r="F19" s="8">
         <v>8000000</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>8000000</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" s="9">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
@@ -1100,7 +1527,7 @@
       <c r="C20" s="7">
         <v>4000000</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>4000000</v>
       </c>
       <c r="E20" s="8">
@@ -1109,11 +1536,14 @@
       <c r="F20" s="8">
         <v>4000000</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>4000000</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" s="9">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
@@ -1123,7 +1553,7 @@
       <c r="C21" s="7">
         <v>224248873.15000001</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>224248873.15000001</v>
       </c>
       <c r="E21" s="8">
@@ -1132,81 +1562,893 @@
       <c r="F21" s="8">
         <v>224248873.15000001</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
+        <v>224248873.15000001</v>
+      </c>
+      <c r="H21" s="9">
         <v>205235785.91</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="7">
-        <v>41704362.840000011</v>
+        <f>'[1]قائمة الدخل'!O36</f>
+        <v>1803626.7499999756</v>
       </c>
       <c r="C22" s="7">
-        <v>31591018.250000037</v>
-      </c>
-      <c r="D22" s="8">
-        <v>18218555.570000034</v>
+        <f>'[1]قائمة الدخل'!Q36</f>
+        <v>10102344.589999976</v>
+      </c>
+      <c r="D22" s="7">
+        <f>'[1]قائمة الدخل'!S36</f>
+        <v>13372462.680000003</v>
       </c>
       <c r="E22" s="8">
-        <v>11129867.850000061</v>
+        <f>'[1]قائمة الدخل'!U36</f>
+        <v>7088687.7199999718</v>
       </c>
       <c r="F22" s="8">
-        <v>5096691.1000000574</v>
-      </c>
-      <c r="G22" s="9">
+        <f>'[1]قائمة الدخل'!W36</f>
+        <v>6033176.7500000028</v>
+      </c>
+      <c r="G22" s="8">
+        <f>'[1]قائمة الدخل'!Y36</f>
+        <v>5096691.0900000576</v>
+      </c>
+      <c r="H22" s="9">
+        <f>'[1]قائمة الدخل'!AA36</f>
         <v>19013087.240000173</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="11">
-        <v>277953235.99000001</v>
+        <f>SUM(B19:B22)</f>
+        <v>238052499.89999998</v>
       </c>
       <c r="C23" s="11">
-        <v>267839891.40000004</v>
-      </c>
-      <c r="D23" s="12">
-        <v>254467428.72000003</v>
+        <f>SUM(C19:C22)</f>
+        <v>246351217.73999998</v>
+      </c>
+      <c r="D23" s="11">
+        <f>SUM(D19:D22)</f>
+        <v>249621335.83000001</v>
       </c>
       <c r="E23" s="12">
-        <v>247378741.00000006</v>
+        <f>SUM(E19:E22)</f>
+        <v>243337560.86999997</v>
       </c>
       <c r="F23" s="12">
-        <v>241345564.25000006</v>
+        <f>SUM(F19:F22)</f>
+        <v>242282049.90000001</v>
       </c>
       <c r="G23" s="12">
+        <f>SUM(G19:G22)</f>
+        <v>241345564.24000007</v>
+      </c>
+      <c r="H23" s="12">
+        <f>SUM(H19:H22)</f>
         <v>236248873.15000015</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="17">
-        <v>623150761.47000015</v>
+      <c r="B24" s="18">
+        <f>B23+B18</f>
+        <v>239309806.32999998</v>
       </c>
       <c r="C24" s="17">
-        <v>517401693.37999994</v>
+        <f>C23+C18</f>
+        <v>247603788.16999999</v>
       </c>
       <c r="D24" s="17">
-        <v>460360235.97999787</v>
+        <f>D18+D23</f>
+        <v>250843901.26000002</v>
       </c>
       <c r="E24" s="17">
-        <v>479285650.77999991</v>
+        <f>E23+E18</f>
+        <v>244529076.12999997</v>
       </c>
       <c r="F24" s="17">
-        <v>542218488.59999907</v>
+        <f>F18+F23</f>
+        <v>243216752.80000001</v>
       </c>
       <c r="G24" s="17">
-        <v>519172592.29000044</v>
+        <f>G23+G18</f>
+        <v>241824206.78000006</v>
+      </c>
+      <c r="H24" s="17">
+        <f>H18+H23</f>
+        <v>237048767.20000017</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G24" xr:uid="{C4E14BED-4A82-49F0-AB48-4A735E1CAC39}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C9DD0B-B807-40B8-A766-55A084718CAF}">
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>46174</v>
+      </c>
+      <c r="C1" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D1" s="2">
+        <v>46113</v>
+      </c>
+      <c r="E1" s="2">
+        <v>46082</v>
+      </c>
+      <c r="F1" s="2">
+        <v>46054</v>
+      </c>
+      <c r="G1" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H1" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <f>[1]الايضاحات!P10</f>
+        <v>28287588.039999999</v>
+      </c>
+      <c r="C2" s="4">
+        <f>[1]الايضاحات!R10</f>
+        <v>27663588.039999999</v>
+      </c>
+      <c r="D2" s="4">
+        <f>[1]الايضاحات!T10</f>
+        <v>27663588.039999999</v>
+      </c>
+      <c r="E2" s="5">
+        <f>[1]الايضاحات!V10</f>
+        <v>25264504.039999999</v>
+      </c>
+      <c r="F2" s="5">
+        <f>[1]الايضاحات!X10</f>
+        <v>25264504.039999999</v>
+      </c>
+      <c r="G2" s="5">
+        <f>[1]الايضاحات!Z10</f>
+        <v>25264504.039999999</v>
+      </c>
+      <c r="H2" s="6">
+        <f>[1]الايضاحات!AB10</f>
+        <v>25264504.039999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7">
+        <f>[1]الايضاحات!P12</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="7">
+        <f>[1]الايضاحات!R12</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <f>[1]الايضاحات!T12</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="8">
+        <f>[1]الايضاحات!V12</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="8">
+        <f>[1]الايضاحات!X12</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="8">
+        <f>[1]الايضاحات!Z12</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <f>[1]الايضاحات!AB12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7">
+        <f>[1]الايضاحات!P13</f>
+        <v>22199177.149999999</v>
+      </c>
+      <c r="C4" s="7">
+        <f>[1]الايضاحات!R13</f>
+        <v>21766987.909999996</v>
+      </c>
+      <c r="D4" s="7">
+        <f>[1]الايضاحات!T13</f>
+        <v>21958105.329999998</v>
+      </c>
+      <c r="E4" s="8">
+        <f>[1]الايضاحات!V13</f>
+        <v>19733077.309999999</v>
+      </c>
+      <c r="F4" s="8">
+        <f>[1]الايضاحات!X13</f>
+        <v>19903916.759999998</v>
+      </c>
+      <c r="G4" s="8">
+        <f>[1]الايضاحات!Z13</f>
+        <v>20074784.07</v>
+      </c>
+      <c r="H4" s="9">
+        <f>[1]الايضاحات!AB13</f>
+        <v>20245724.849999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11">
+        <f>SUM(B2:B4)</f>
+        <v>50486765.189999998</v>
+      </c>
+      <c r="C5" s="11">
+        <f>SUM(C2:C4)</f>
+        <v>49430575.949999996</v>
+      </c>
+      <c r="D5" s="11">
+        <f>SUM(D2:D4)</f>
+        <v>49621693.369999997</v>
+      </c>
+      <c r="E5" s="12">
+        <f>SUM(E2:E4)</f>
+        <v>44997581.349999994</v>
+      </c>
+      <c r="F5" s="12">
+        <f>SUM(F2:F4)</f>
+        <v>45168420.799999997</v>
+      </c>
+      <c r="G5" s="12">
+        <f>SUM(G2:G4)</f>
+        <v>45339288.109999999</v>
+      </c>
+      <c r="H5" s="12">
+        <f>SUM(H2:H4)</f>
+        <v>45510228.890000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7">
+        <f>[1]الايضاحات!P23</f>
+        <v>14943580.889999989</v>
+      </c>
+      <c r="C6" s="7">
+        <f>[1]الايضاحات!R23</f>
+        <v>13711093.810000001</v>
+      </c>
+      <c r="D6" s="7">
+        <f>[1]الايضاحات!T23</f>
+        <v>16704395.5</v>
+      </c>
+      <c r="E6" s="8">
+        <f>[1]الايضاحات!V23</f>
+        <v>7370521.9300000072</v>
+      </c>
+      <c r="F6" s="8">
+        <f>[1]الايضاحات!X23</f>
+        <v>22488344.050000008</v>
+      </c>
+      <c r="G6" s="8">
+        <f>[1]الايضاحات!Z23</f>
+        <v>40175935.459999979</v>
+      </c>
+      <c r="H6" s="9">
+        <f>[1]الايضاحات!AB23</f>
+        <v>48312473.840000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7">
+        <f>[1]الايضاحات!P39</f>
+        <v>-0.30999999865889549</v>
+      </c>
+      <c r="C7" s="7">
+        <f>[1]الايضاحات!R39</f>
+        <v>-0.30999999865889549</v>
+      </c>
+      <c r="D7" s="7">
+        <f>[1]الايضاحات!T39</f>
+        <v>-0.30999999865889549</v>
+      </c>
+      <c r="E7" s="8">
+        <f>[1]الايضاحات!V39</f>
+        <v>-0.30999999865889549</v>
+      </c>
+      <c r="F7" s="8">
+        <f>[1]الايضاحات!X39</f>
+        <v>-0.30999999865889549</v>
+      </c>
+      <c r="G7" s="8">
+        <f>[1]الايضاحات!Z39</f>
+        <v>-0.30999999865889549</v>
+      </c>
+      <c r="H7" s="9">
+        <f>[1]الايضاحات!AB39</f>
+        <v>-0.30999999865889499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7">
+        <f>[1]الايضاحات!P49</f>
+        <v>21865000.519999959</v>
+      </c>
+      <c r="C8" s="7">
+        <f>[1]الايضاحات!R49</f>
+        <v>54827135.009999961</v>
+      </c>
+      <c r="D8" s="7">
+        <f>[1]الايضاحات!T49</f>
+        <v>41244559.470000014</v>
+      </c>
+      <c r="E8" s="8">
+        <f>[1]الايضاحات!V49</f>
+        <v>31136322.539999995</v>
+      </c>
+      <c r="F8" s="8">
+        <f>[1]الايضاحات!X49</f>
+        <v>9514470.6399999894</v>
+      </c>
+      <c r="G8" s="8">
+        <f>[1]الايضاحات!Z49</f>
+        <v>10873933.310000006</v>
+      </c>
+      <c r="H8" s="9">
+        <f>[1]الايضاحات!AB49</f>
+        <v>30131838.569999985</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7">
+        <f>[1]الايضاحات!P53</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="7">
+        <f>[1]الايضاحات!R53</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="7">
+        <f>[1]الايضاحات!T53</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="8">
+        <f>[1]الايضاحات!V53</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="8">
+        <f>[1]الايضاحات!X53</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <f>[1]الايضاحات!Z53</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <f>[1]الايضاحات!AB53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7">
+        <v>3637923.2</v>
+      </c>
+      <c r="C10" s="7">
+        <f>[1]الايضاحات!R59</f>
+        <v>3416615.87</v>
+      </c>
+      <c r="D10" s="7">
+        <f>[1]الايضاحات!T59</f>
+        <v>3637923.2</v>
+      </c>
+      <c r="E10" s="8">
+        <f>[1]الايضاحات!V59</f>
+        <v>3637923.2</v>
+      </c>
+      <c r="F10" s="8">
+        <f>[1]الايضاحات!X59</f>
+        <v>3404110.7</v>
+      </c>
+      <c r="G10" s="8">
+        <f>[1]الايضاحات!Z59</f>
+        <v>3636923.24</v>
+      </c>
+      <c r="H10" s="9">
+        <f>[1]الايضاحات!AB59</f>
+        <v>3636923.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="11">
+        <f>SUM(B6:B10)</f>
+        <v>40446504.299999952</v>
+      </c>
+      <c r="C11" s="11">
+        <f>SUM(C6:C10)</f>
+        <v>71954844.379999965</v>
+      </c>
+      <c r="D11" s="11">
+        <f>SUM(D6:D10)</f>
+        <v>61586877.860000014</v>
+      </c>
+      <c r="E11" s="12">
+        <f>SUM(E6:E10)</f>
+        <v>42144767.360000007</v>
+      </c>
+      <c r="F11" s="12">
+        <f>SUM(F6:F10)</f>
+        <v>35406925.079999998</v>
+      </c>
+      <c r="G11" s="12">
+        <f>SUM(G6:G10)</f>
+        <v>54686791.699999981</v>
+      </c>
+      <c r="H11" s="12">
+        <f>SUM(H6:H10)</f>
+        <v>82081235.339999989</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="14">
+        <f>B11+B5</f>
+        <v>90933269.48999995</v>
+      </c>
+      <c r="C12" s="14">
+        <f>C11+C5</f>
+        <v>121385420.32999995</v>
+      </c>
+      <c r="D12" s="15">
+        <f>D5+D11</f>
+        <v>111208571.23000002</v>
+      </c>
+      <c r="E12" s="15">
+        <f>E11+E5</f>
+        <v>87142348.710000008</v>
+      </c>
+      <c r="F12" s="15">
+        <f>F11+F5</f>
+        <v>80575345.879999995</v>
+      </c>
+      <c r="G12" s="15">
+        <f>G11+G5</f>
+        <v>100026079.80999997</v>
+      </c>
+      <c r="H12" s="15">
+        <f>H5+H11</f>
+        <v>127591464.22999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7">
+        <f>[1]الايضاحات!P69</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="7">
+        <f>[1]الايضاحات!R69</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="7">
+        <f>[1]الايضاحات!T69</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <f>[1]الايضاحات!V69</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <f>[1]الايضاحات!X69</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <f>[1]الايضاحات!Z69</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <f>[1]الايضاحات!AB69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7">
+        <f>[1]الايضاحات!P90</f>
+        <v>457416.99000000948</v>
+      </c>
+      <c r="C14" s="7">
+        <f>[1]الايضاحات!R90</f>
+        <v>452680.99000000948</v>
+      </c>
+      <c r="D14" s="7">
+        <f>[1]الايضاحات!T90</f>
+        <v>422675.99000000948</v>
+      </c>
+      <c r="E14" s="8">
+        <f>[1]الايضاحات!V90</f>
+        <v>391625.81999999279</v>
+      </c>
+      <c r="F14" s="8">
+        <f>[1]الايضاحات!X90</f>
+        <v>134813.46000000829</v>
+      </c>
+      <c r="G14" s="8">
+        <f>[1]الايضاحات!Z90</f>
+        <v>-321246.90000000602</v>
+      </c>
+      <c r="H14" s="9">
+        <f>[1]الايضاحات!AB90</f>
+        <v>4.6100000143051147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7">
+        <f>[1]الايضاحات!P104</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="7">
+        <f>[1]الايضاحات!R104</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="7">
+        <f>[1]الايضاحات!T104</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <f>[1]الايضاحات!V104</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <f>[1]الايضاحات!X104</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <f>[1]الايضاحات!Z104</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <f>[1]الايضاحات!AB104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8">
+        <f>727553+59413</f>
+        <v>786966</v>
+      </c>
+      <c r="C16" s="8">
+        <f>727553+59413</f>
+        <v>786966</v>
+      </c>
+      <c r="D16" s="8">
+        <f>727553+59413</f>
+        <v>786966</v>
+      </c>
+      <c r="E16" s="8">
+        <f>727553+59413</f>
+        <v>786966</v>
+      </c>
+      <c r="F16" s="8">
+        <f>727553+59413</f>
+        <v>786966</v>
+      </c>
+      <c r="G16" s="8">
+        <f>727553+59413</f>
+        <v>786966</v>
+      </c>
+      <c r="H16" s="9">
+        <f>727553+59413</f>
+        <v>786966</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="7">
+        <f>[1]الايضاحات!P112</f>
+        <v>12923.44</v>
+      </c>
+      <c r="C17" s="7">
+        <f>[1]الايضاحات!R112</f>
+        <v>12923.44</v>
+      </c>
+      <c r="D17" s="7">
+        <f>[1]الايضاحات!T112</f>
+        <v>12923.44</v>
+      </c>
+      <c r="E17" s="8">
+        <f>[1]الايضاحات!V112</f>
+        <v>12923.44</v>
+      </c>
+      <c r="F17" s="8">
+        <f>[1]الايضاحات!X112</f>
+        <v>12923.44</v>
+      </c>
+      <c r="G17" s="8">
+        <f>[1]الايضاحات!Z112</f>
+        <v>12923.44</v>
+      </c>
+      <c r="H17" s="9">
+        <f>[1]الايضاحات!AB112</f>
+        <v>12923.44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="11">
+        <f>SUM(B13:B17)</f>
+        <v>1257306.4300000095</v>
+      </c>
+      <c r="C18" s="11">
+        <f>SUM(C13:C17)</f>
+        <v>1252570.4300000095</v>
+      </c>
+      <c r="D18" s="11">
+        <f>SUM(D13:D17)</f>
+        <v>1222565.4300000095</v>
+      </c>
+      <c r="E18" s="12">
+        <f>SUM(E13:E17)</f>
+        <v>1191515.2599999928</v>
+      </c>
+      <c r="F18" s="12">
+        <f>SUM(F13:F17)</f>
+        <v>934702.90000000829</v>
+      </c>
+      <c r="G18" s="12">
+        <f>SUM(G13:G17)</f>
+        <v>478642.53999999398</v>
+      </c>
+      <c r="H18" s="12">
+        <f>SUM(H13:H17)</f>
+        <v>799894.05000001425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7">
+        <v>8000000</v>
+      </c>
+      <c r="C19" s="7">
+        <v>8000000</v>
+      </c>
+      <c r="D19" s="7">
+        <v>8000000</v>
+      </c>
+      <c r="E19" s="8">
+        <v>8000000</v>
+      </c>
+      <c r="F19" s="8">
+        <v>8000000</v>
+      </c>
+      <c r="G19" s="8">
+        <v>8000000</v>
+      </c>
+      <c r="H19" s="9">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7">
+        <v>4000000</v>
+      </c>
+      <c r="C20" s="7">
+        <v>4000000</v>
+      </c>
+      <c r="D20" s="7">
+        <v>4000000</v>
+      </c>
+      <c r="E20" s="8">
+        <v>4000000</v>
+      </c>
+      <c r="F20" s="8">
+        <v>4000000</v>
+      </c>
+      <c r="G20" s="8">
+        <v>4000000</v>
+      </c>
+      <c r="H20" s="9">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="7">
+        <v>224248873.15000001</v>
+      </c>
+      <c r="C21" s="7">
+        <v>224248873.15000001</v>
+      </c>
+      <c r="D21" s="7">
+        <v>224248873.15000001</v>
+      </c>
+      <c r="E21" s="8">
+        <v>224248873.15000001</v>
+      </c>
+      <c r="F21" s="8">
+        <v>224248873.15000001</v>
+      </c>
+      <c r="G21" s="8">
+        <v>224248873.15000001</v>
+      </c>
+      <c r="H21" s="9">
+        <v>205235785.91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="7">
+        <f>'[1]قائمة الدخل'!O36</f>
+        <v>1803626.7499999756</v>
+      </c>
+      <c r="C22" s="7">
+        <f>'[1]قائمة الدخل'!Q36</f>
+        <v>10102344.589999976</v>
+      </c>
+      <c r="D22" s="7">
+        <f>'[1]قائمة الدخل'!S36</f>
+        <v>13372462.680000003</v>
+      </c>
+      <c r="E22" s="8">
+        <f>'[1]قائمة الدخل'!U36</f>
+        <v>7088687.7199999718</v>
+      </c>
+      <c r="F22" s="8">
+        <f>'[1]قائمة الدخل'!W36</f>
+        <v>6033176.7500000028</v>
+      </c>
+      <c r="G22" s="8">
+        <f>'[1]قائمة الدخل'!Y36</f>
+        <v>5096691.0900000576</v>
+      </c>
+      <c r="H22" s="9">
+        <f>'[1]قائمة الدخل'!AA36</f>
+        <v>19013087.240000173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="11">
+        <f>SUM(B19:B22)</f>
+        <v>238052499.89999998</v>
+      </c>
+      <c r="C23" s="11">
+        <f>SUM(C19:C22)</f>
+        <v>246351217.73999998</v>
+      </c>
+      <c r="D23" s="11">
+        <f>SUM(D19:D22)</f>
+        <v>249621335.83000001</v>
+      </c>
+      <c r="E23" s="12">
+        <f>SUM(E19:E22)</f>
+        <v>243337560.86999997</v>
+      </c>
+      <c r="F23" s="12">
+        <f>SUM(F19:F22)</f>
+        <v>242282049.90000001</v>
+      </c>
+      <c r="G23" s="12">
+        <f>SUM(G19:G22)</f>
+        <v>241345564.24000007</v>
+      </c>
+      <c r="H23" s="12">
+        <f>SUM(H19:H22)</f>
+        <v>236248873.15000015</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="18">
+        <f>B23+B18</f>
+        <v>239309806.32999998</v>
+      </c>
+      <c r="C24" s="17">
+        <f>C23+C18</f>
+        <v>247603788.16999999</v>
+      </c>
+      <c r="D24" s="17">
+        <f>D18+D23</f>
+        <v>250843901.26000002</v>
+      </c>
+      <c r="E24" s="17">
+        <f>E23+E18</f>
+        <v>244529076.12999997</v>
+      </c>
+      <c r="F24" s="17">
+        <f>F18+F23</f>
+        <v>243216752.80000001</v>
+      </c>
+      <c r="G24" s="17">
+        <f>G23+G18</f>
+        <v>241824206.78000006</v>
+      </c>
+      <c r="H24" s="17">
+        <f>H18+H23</f>
+        <v>237048767.20000017</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AA24" xr:uid="{48C9DD0B-B807-40B8-A766-55A084718CAF}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/5-2026.xlsx
+++ b/5-2026.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\balanceSheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1856A222-EC3A-4794-B598-C2FD8CD860C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC45B258-BA4B-4CA8-AF66-A884944263BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{C7DBF94B-76D0-4DB1-B5F9-1612F1925133}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{22711B75-76D9-4178-BA38-3EFE03212E7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -112,10 +112,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="m\-yyyy"/>
-    <numFmt numFmtId="165" formatCode="B1mmm\-yy"/>
+    <numFmt numFmtId="165" formatCode="m\-yyyy"/>
+    <numFmt numFmtId="166" formatCode="B1mmm\-yy"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0\ _ج_._م_._‏_-;\-* #,##0\ _ج_._م_._‏_-;_-* &quot;-&quot;\ _ج_._م_._‏_-;_-@_-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -181,6 +182,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <u/>
       <sz val="14"/>
       <name val="Arial"/>
@@ -190,14 +199,6 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -286,12 +287,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -300,6 +313,9 @@
     <xf numFmtId="43" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="4" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -324,23 +340,32 @@
     <xf numFmtId="4" fontId="7" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -656,640 +681,719 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4E14BED-4A82-49F0-AB48-4A735E1CAC39}">
-  <dimension ref="A1:H24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2387683F-6A26-4967-9F2B-AE7C8F037119}">
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5" style="4" customWidth="1"/>
+    <col min="2" max="3" width="20.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="15.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="6">
+        <v>46204</v>
+      </c>
+      <c r="C1" s="6">
         <v>46174</v>
       </c>
-      <c r="C1" s="2">
+      <c r="D1" s="6">
         <v>46143</v>
       </c>
-      <c r="D1" s="2">
+      <c r="E1" s="6">
         <v>46113</v>
       </c>
-      <c r="E1" s="2">
+      <c r="F1" s="6">
         <v>46082</v>
       </c>
-      <c r="F1" s="2">
+      <c r="G1" s="6">
         <v>46054</v>
       </c>
-      <c r="G1" s="2">
+      <c r="H1" s="6">
         <v>46023</v>
       </c>
-      <c r="H1" s="2">
+      <c r="I1" s="6">
         <v>45992</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="8">
+        <v>23560668.130000003</v>
+      </c>
+      <c r="C2" s="8">
         <v>22199177.149999999</v>
       </c>
-      <c r="C2" s="4">
+      <c r="D2" s="8">
         <v>21766987.909999996</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="8">
         <v>21958105.329999998</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="10">
         <v>19733077.309999999</v>
       </c>
-      <c r="F2" s="5">
+      <c r="G2" s="10">
         <v>19903916.759999998</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H2" s="10">
         <v>20074784.07</v>
       </c>
-      <c r="H2" s="6">
+      <c r="I2" s="11">
         <v>20245724.849999998</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="12">
         <v>2373214.15</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="12">
+        <v>2373214.15</v>
+      </c>
+      <c r="D3" s="12">
         <v>2357614.15</v>
       </c>
-      <c r="D3" s="7">
+      <c r="E3" s="12">
         <v>2346114.15</v>
       </c>
-      <c r="E3" s="8">
+      <c r="F3" s="13">
         <v>2232984.15</v>
       </c>
-      <c r="F3" s="8">
+      <c r="G3" s="13">
         <v>2200362.15</v>
       </c>
-      <c r="G3" s="8">
+      <c r="H3" s="13">
         <v>1884602.5</v>
       </c>
-      <c r="H3" s="9">
+      <c r="I3" s="14">
         <v>1884602.5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="12">
         <v>596741</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="12">
         <v>596741</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="12">
         <v>596741</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="12">
         <v>596741</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="13">
         <v>596741</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="13">
         <v>596741</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="13">
         <v>596741</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="I4" s="14">
+        <v>596741</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="16">
+        <v>26530623.280000001</v>
+      </c>
+      <c r="C5" s="16">
         <v>25169132.299999997</v>
       </c>
-      <c r="C5" s="11">
+      <c r="D5" s="16">
         <v>24721343.059999995</v>
       </c>
-      <c r="D5" s="11">
+      <c r="E5" s="16">
         <v>24900960.479999997</v>
       </c>
-      <c r="E5" s="12">
+      <c r="F5" s="17">
         <v>22562802.459999997</v>
       </c>
-      <c r="F5" s="12">
+      <c r="G5" s="17">
         <v>22701019.909999996</v>
       </c>
-      <c r="G5" s="12">
+      <c r="H5" s="17">
         <v>22556127.57</v>
       </c>
-      <c r="H5" s="12">
+      <c r="I5" s="17">
         <v>22727068.349999998</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="12">
+        <v>309138879.46999943</v>
+      </c>
+      <c r="C6" s="12">
         <v>309527001.88999999</v>
       </c>
-      <c r="C6" s="7">
+      <c r="D6" s="12">
         <v>307962482.93999964</v>
       </c>
-      <c r="D6" s="7">
+      <c r="E6" s="12">
         <v>251497026.58999923</v>
       </c>
-      <c r="E6" s="8">
+      <c r="F6" s="13">
         <v>216736145.83000055</v>
       </c>
-      <c r="F6" s="8">
+      <c r="G6" s="13">
         <v>246421191.35999998</v>
       </c>
-      <c r="G6" s="8">
+      <c r="H6" s="13">
         <v>276755395.22999948</v>
       </c>
-      <c r="H6" s="9">
+      <c r="I6" s="14">
         <v>263703635.98999962</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7">
-        <v>64696992.730000049</v>
-      </c>
-      <c r="C7" s="7">
-        <v>53595675.89000012</v>
-      </c>
-      <c r="D7" s="7">
-        <v>35170513.569999754</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="B7" s="12">
+        <v>70184274.540000036</v>
+      </c>
+      <c r="C7" s="12">
+        <v>59455323.910000071</v>
+      </c>
+      <c r="D7" s="12">
+        <v>53625668.39000012</v>
+      </c>
+      <c r="E7" s="12">
+        <v>35200506.069999754</v>
+      </c>
+      <c r="F7" s="13">
         <v>36391015.480000034</v>
       </c>
-      <c r="F7" s="8">
+      <c r="G7" s="13">
         <v>35044469.309999794</v>
       </c>
-      <c r="G7" s="8">
+      <c r="H7" s="13">
         <v>40312392.319999546</v>
       </c>
-      <c r="H7" s="9">
+      <c r="I7" s="14">
         <v>35899338.66000022</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="12">
+        <v>51209264.369999841</v>
+      </c>
+      <c r="C8" s="12">
         <v>59369229.920000523</v>
       </c>
-      <c r="C8" s="7">
+      <c r="D8" s="12">
         <v>88773553.039999709</v>
       </c>
-      <c r="D8" s="7">
+      <c r="E8" s="12">
         <v>80049672.870000184</v>
       </c>
-      <c r="E8" s="8">
+      <c r="F8" s="13">
         <v>69103414.059999168</v>
       </c>
-      <c r="F8" s="8">
+      <c r="G8" s="13">
         <v>62152170.890000343</v>
       </c>
-      <c r="G8" s="8">
+      <c r="H8" s="13">
         <v>73211384.189999923</v>
       </c>
-      <c r="H8" s="9">
+      <c r="I8" s="14">
         <v>55796550.240000226</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
-        <v>149692124.43999955</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="B9" s="12">
+        <v>172600094.34999996</v>
+      </c>
+      <c r="C9" s="12">
+        <v>149690756.01999947</v>
+      </c>
+      <c r="D9" s="12">
         <v>144670090.74999979</v>
       </c>
-      <c r="D9" s="7">
+      <c r="E9" s="12">
         <v>122145542.94999963</v>
       </c>
-      <c r="E9" s="8">
+      <c r="F9" s="13">
         <v>111928881.3599996</v>
       </c>
-      <c r="F9" s="8">
+      <c r="G9" s="13">
         <v>109562688.63999996</v>
       </c>
-      <c r="G9" s="8">
+      <c r="H9" s="13">
         <v>125746266.17999986</v>
       </c>
-      <c r="H9" s="9">
+      <c r="I9" s="14">
         <v>137039113.50999942</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="12">
+        <v>21646985.150000002</v>
+      </c>
+      <c r="C10" s="12">
         <v>3637923.2</v>
       </c>
-      <c r="C10" s="7">
+      <c r="D10" s="12">
         <v>3416615.87</v>
       </c>
-      <c r="D10" s="7">
+      <c r="E10" s="12">
         <v>3637923.2</v>
       </c>
-      <c r="E10" s="8">
+      <c r="F10" s="13">
         <v>3637923.2</v>
       </c>
-      <c r="F10" s="8">
+      <c r="G10" s="13">
         <v>3404110.7</v>
       </c>
-      <c r="G10" s="8">
+      <c r="H10" s="13">
         <v>3636923.24</v>
       </c>
-      <c r="H10" s="9">
+      <c r="I10" s="14">
         <v>4006885.54</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:9" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="11">
-        <v>586923272.18000019</v>
-      </c>
-      <c r="C11" s="11">
-        <v>598418418.48999929</v>
-      </c>
-      <c r="D11" s="11">
-        <v>492500679.17999882</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="B11" s="16">
+        <v>624779497.87999928</v>
+      </c>
+      <c r="C11" s="16">
+        <v>581680234.94000018</v>
+      </c>
+      <c r="D11" s="16">
+        <v>598448410.98999929</v>
+      </c>
+      <c r="E11" s="16">
+        <v>492530671.67999882</v>
+      </c>
+      <c r="F11" s="17">
         <v>437797379.92999935</v>
       </c>
-      <c r="F11" s="12">
+      <c r="G11" s="17">
         <v>456584630.90000004</v>
       </c>
-      <c r="G11" s="12">
+      <c r="H11" s="17">
         <v>519662361.15999877</v>
       </c>
-      <c r="H11" s="12">
+      <c r="I11" s="17">
         <v>496445523.93999952</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:9" s="20" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="14">
-        <v>612092404.48000014</v>
-      </c>
-      <c r="C12" s="14">
-        <v>623139761.54999924</v>
-      </c>
-      <c r="D12" s="15">
-        <v>517401639.65999883</v>
-      </c>
-      <c r="E12" s="15">
+      <c r="B12" s="21">
+        <v>651310121.15999925</v>
+      </c>
+      <c r="C12" s="21">
+        <v>606849367.24000013</v>
+      </c>
+      <c r="D12" s="21">
+        <v>623169754.04999924</v>
+      </c>
+      <c r="E12" s="22">
+        <v>517431632.15999883</v>
+      </c>
+      <c r="F12" s="22">
         <v>460360182.38999933</v>
       </c>
-      <c r="F12" s="15">
+      <c r="G12" s="22">
         <v>479285650.81000006</v>
       </c>
-      <c r="G12" s="15">
+      <c r="H12" s="22">
         <v>542218488.72999883</v>
       </c>
-      <c r="H12" s="15">
+      <c r="I12" s="22">
         <v>519172592.28999954</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="7">
-        <v>217698395.41000026</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="B13" s="12">
+        <v>253155600.78000042</v>
+      </c>
+      <c r="C13" s="12">
+        <v>216556629.12999955</v>
+      </c>
+      <c r="D13" s="12">
         <v>221490803.47</v>
       </c>
-      <c r="D13" s="7">
+      <c r="E13" s="12">
         <v>120354247.44999973</v>
       </c>
-      <c r="E13" s="8">
+      <c r="F13" s="13">
         <v>105458756.66999979</v>
       </c>
-      <c r="F13" s="8">
+      <c r="G13" s="13">
         <v>133665877.53000003</v>
       </c>
-      <c r="G13" s="8">
+      <c r="H13" s="13">
         <v>177227503.53999999</v>
       </c>
-      <c r="H13" s="9">
+      <c r="I13" s="14">
         <v>148043033.26000029</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="7">
-        <v>17145192.989999995</v>
-      </c>
-      <c r="C14" s="7">
-        <v>17987661.130000014</v>
-      </c>
-      <c r="D14" s="7">
-        <v>24918599.720000021</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="B14" s="12">
+        <v>15250449.870000014</v>
+      </c>
+      <c r="C14" s="12">
+        <v>12386398.509999959</v>
+      </c>
+      <c r="D14" s="12">
+        <v>17960661.13000001</v>
+      </c>
+      <c r="E14" s="12">
+        <v>24891599.720000021</v>
+      </c>
+      <c r="F14" s="13">
         <v>21895473.599999938</v>
       </c>
-      <c r="F14" s="8">
+      <c r="G14" s="13">
         <v>24608773.970000006</v>
       </c>
-      <c r="G14" s="8">
+      <c r="H14" s="13">
         <v>28574676.589999989</v>
       </c>
-      <c r="H14" s="9">
+      <c r="I14" s="14">
         <v>26189842.269999973</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="12">
+        <v>101654934.77000012</v>
+      </c>
+      <c r="C15" s="12">
         <v>96198307.679999903</v>
       </c>
-      <c r="C15" s="7">
+      <c r="D15" s="12">
         <v>104414415.23000011</v>
       </c>
-      <c r="D15" s="7">
+      <c r="E15" s="12">
         <v>102984255.44000015</v>
       </c>
-      <c r="E15" s="8">
+      <c r="F15" s="13">
         <v>77233877.720000073</v>
       </c>
-      <c r="F15" s="8">
+      <c r="G15" s="13">
         <v>72327612.63000001</v>
       </c>
-      <c r="G15" s="8">
+      <c r="H15" s="13">
         <v>93766086.059999973</v>
       </c>
-      <c r="H15" s="9">
+      <c r="I15" s="14">
         <v>107449108.75</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="13">
         <v>786966</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="13">
         <v>786966</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="13">
         <v>786966</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="13">
         <v>786966</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="13">
         <v>786966</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="13">
         <v>786966</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="13">
         <v>786966</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="I16" s="14">
+        <v>786966</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="12">
+        <v>517682.89999872731</v>
+      </c>
+      <c r="C17" s="12">
         <v>517679.67000000045</v>
       </c>
-      <c r="C17" s="7">
+      <c r="D17" s="12">
         <v>517679.73999911832</v>
       </c>
-      <c r="D17" s="7">
+      <c r="E17" s="12">
         <v>517679.65999889659</v>
       </c>
-      <c r="E17" s="8">
+      <c r="F17" s="13">
         <v>517679.64999807166</v>
       </c>
-      <c r="F17" s="8">
+      <c r="G17" s="13">
         <v>517679.6499998002</v>
       </c>
-      <c r="G17" s="8">
+      <c r="H17" s="13">
         <v>517692.1599990754</v>
       </c>
-      <c r="H17" s="9">
+      <c r="I17" s="14">
         <v>454768.86000001483</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:10" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="11">
-        <v>332346541.75000018</v>
-      </c>
-      <c r="C18" s="11">
-        <v>345197525.56999928</v>
-      </c>
-      <c r="D18" s="11">
-        <v>249561748.26999879</v>
-      </c>
-      <c r="E18" s="12">
+      <c r="B18" s="16">
+        <v>371365634.31999928</v>
+      </c>
+      <c r="C18" s="16">
+        <v>326445980.98999941</v>
+      </c>
+      <c r="D18" s="16">
+        <v>345170525.56999928</v>
+      </c>
+      <c r="E18" s="16">
+        <v>249534748.26999879</v>
+      </c>
+      <c r="F18" s="17">
         <v>205892753.63999787</v>
       </c>
-      <c r="F18" s="12">
+      <c r="G18" s="17">
         <v>231906909.77999985</v>
       </c>
-      <c r="G18" s="12">
+      <c r="H18" s="17">
         <v>300872924.34999901</v>
       </c>
-      <c r="H18" s="12">
+      <c r="I18" s="17">
         <v>282923719.14000028</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="J18" s="23"/>
+    </row>
+    <row r="19" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="12">
         <v>8000000</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="12">
         <v>8000000</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="12">
         <v>8000000</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="12">
         <v>8000000</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="13">
         <v>8000000</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="13">
         <v>8000000</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="13">
         <v>8000000</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="I19" s="14">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="12">
         <v>4000000</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="12">
         <v>4000000</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="12">
         <v>4000000</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="12">
         <v>4000000</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="13">
         <v>4000000</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="13">
         <v>4000000</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="13">
         <v>4000000</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="I20" s="14">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="12">
         <v>224248873.15000001</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="12">
         <v>224248873.15000001</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="12">
         <v>224248873.15000001</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="12">
         <v>224248873.15000001</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="13">
         <v>224248873.15000001</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="13">
         <v>224248873.15000001</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="13">
+        <v>224248873.15000001</v>
+      </c>
+      <c r="I21" s="14">
         <v>205235785.91</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="7">
-        <v>43496989.579999991</v>
-      </c>
-      <c r="C22" s="7">
-        <v>41693362.830000013</v>
-      </c>
-      <c r="D22" s="7">
-        <v>31591018.240000036</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="B22" s="12">
+        <v>43695613.690000013</v>
+      </c>
+      <c r="C22" s="12">
+        <v>44154513.079999991</v>
+      </c>
+      <c r="D22" s="12">
+        <v>41750355.330000013</v>
+      </c>
+      <c r="E22" s="12">
+        <v>31648010.740000036</v>
+      </c>
+      <c r="F22" s="13">
         <v>18218555.560000032</v>
       </c>
-      <c r="F22" s="8">
+      <c r="G22" s="13">
         <v>11129867.840000059</v>
       </c>
-      <c r="G22" s="8">
+      <c r="H22" s="13">
         <v>5096691.0900000576</v>
       </c>
-      <c r="H22" s="9">
+      <c r="I22" s="14">
         <v>19013087.240000173</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:10" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="11">
-        <v>279745862.73000002</v>
-      </c>
-      <c r="C23" s="11">
-        <v>277942235.98000002</v>
-      </c>
-      <c r="D23" s="11">
-        <v>267839891.39000005</v>
-      </c>
-      <c r="E23" s="12">
+      <c r="B23" s="16">
+        <v>279944486.84000003</v>
+      </c>
+      <c r="C23" s="16">
+        <v>280403386.23000002</v>
+      </c>
+      <c r="D23" s="16">
+        <v>277999228.48000002</v>
+      </c>
+      <c r="E23" s="16">
+        <v>267896883.89000005</v>
+      </c>
+      <c r="F23" s="17">
         <v>254467428.71000004</v>
       </c>
-      <c r="F23" s="12">
+      <c r="G23" s="17">
         <v>247378740.99000007</v>
       </c>
-      <c r="G23" s="12">
+      <c r="H23" s="17">
         <v>241345564.24000007</v>
       </c>
-      <c r="H23" s="12">
+      <c r="I23" s="17">
         <v>236248873.15000015</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+    <row r="24" spans="1:10" s="25" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="18">
-        <v>612092404.48000026</v>
-      </c>
-      <c r="C24" s="17">
-        <v>623139761.54999924</v>
-      </c>
-      <c r="D24" s="17">
-        <v>517401639.65999883</v>
-      </c>
-      <c r="E24" s="17">
+      <c r="B24" s="26">
+        <v>651310121.15999937</v>
+      </c>
+      <c r="C24" s="26">
+        <v>606849367.21999943</v>
+      </c>
+      <c r="D24" s="26">
+        <v>623169754.04999924</v>
+      </c>
+      <c r="E24" s="26">
+        <v>517431632.15999883</v>
+      </c>
+      <c r="F24" s="26">
         <v>460360182.34999788</v>
       </c>
-      <c r="F24" s="17">
+      <c r="G24" s="26">
         <v>479285650.76999992</v>
       </c>
-      <c r="G24" s="17">
+      <c r="H24" s="26">
         <v>542218488.58999908</v>
       </c>
-      <c r="H24" s="17">
+      <c r="I24" s="26">
         <v>519172592.29000044</v>
       </c>
     </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D27" s="1"/>
+      <c r="E27" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G24" xr:uid="{C4E14BED-4A82-49F0-AB48-4A735E1CAC39}"/>
+  <autoFilter ref="A1:AB35" xr:uid="{2387683F-6A26-4967-9F2B-AE7C8F037119}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>